--- a/results/supplementary/tables_submission/TableS1_hub_genes.xlsx
+++ b/results/supplementary/tables_submission/TableS1_hub_genes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t xml:space="preserve">Gene</t>
   </si>
@@ -61,18 +61,6 @@
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4909</t>
-  </si>
-  <si>
     <t xml:space="preserve">Both</t>
   </si>
   <si>
@@ -82,18 +70,6 @@
     <t xml:space="preserve">Tetracycline</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4364</t>
-  </si>
-  <si>
     <t xml:space="preserve">aac(6')</t>
   </si>
   <si>
@@ -106,36 +82,12 @@
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4444</t>
-  </si>
-  <si>
     <t xml:space="preserve">adec</t>
   </si>
   <si>
     <t xml:space="preserve">Efflux pump (AdeABC)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4889</t>
-  </si>
-  <si>
     <t xml:space="preserve">Connectivity</t>
   </si>
   <si>
@@ -148,36 +100,12 @@
     <t xml:space="preserve">C1 (Beta-lactam/Aminoglycoside)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333</t>
-  </si>
-  <si>
     <t xml:space="preserve">dfra</t>
   </si>
   <si>
     <t xml:space="preserve">Trimethoprim</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3111</t>
-  </si>
-  <si>
     <t xml:space="preserve">arma</t>
   </si>
   <si>
@@ -190,15 +118,6 @@
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5034</t>
-  </si>
-  <si>
     <t xml:space="preserve">ftsi</t>
   </si>
   <si>
@@ -208,18 +127,6 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2143</t>
-  </si>
-  <si>
     <t xml:space="preserve">blaoxa_23like</t>
   </si>
   <si>
@@ -230,28 +137,17 @@
   </si>
   <si>
     <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1905</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,38 +171,34 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Ubuntu"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
+      <sz val="12"/>
+      <name val="Ubuntu"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Ubuntu"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E4057"/>
-        <bgColor rgb="FF333399"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -350,21 +242,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -376,66 +276,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF2E4057"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -620,306 +460,307 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.9249</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.9199</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
+      <c r="E4" s="5" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>38</v>
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.8854</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.8819</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.8174</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>38</v>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.6719</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
